--- a/gte/nodes/P/compresor_blade_self_frequency.xlsx
+++ b/gte/nodes/P/compresor_blade_self_frequency.xlsx
@@ -552,58 +552,58 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>67.648260139678356</v>
+        <v>58.47162127718066</v>
       </c>
       <c r="C3">
-        <v>423.97500869716822</v>
+        <v>366.46184378346771</v>
       </c>
       <c r="D3">
-        <v>1187.2617216241206</v>
+        <v>1026.2069948341637</v>
       </c>
       <c r="E3">
-        <v>2328.3027845407523</v>
+        <v>2012.4632674243869</v>
       </c>
       <c r="F3">
-        <v>3847.2721274377204</v>
+        <v>3325.3809975497929</v>
       </c>
       <c r="G3">
-        <v>5745.6817039620937</v>
+        <v>4966.2670389396208</v>
       </c>
       <c r="H3">
-        <v>289.23441368392548</v>
+        <v>290.61056770124219</v>
       </c>
       <c r="I3">
-        <v>867.70324105177633</v>
+        <v>871.83170310372657</v>
       </c>
       <c r="J3">
-        <v>1446.1720684196271</v>
+        <v>1453.052838506211</v>
       </c>
       <c r="K3">
-        <v>2024.6408957874783</v>
+        <v>2034.2739739086953</v>
       </c>
       <c r="L3">
-        <v>2603.1097231553285</v>
+        <v>2615.4951093111795</v>
       </c>
       <c r="M3">
-        <v>3181.5785505231797</v>
+        <v>3196.7162447136639</v>
       </c>
       <c r="N3">
-        <v>578.468827367851</v>
+        <v>581.22113540248438</v>
       </c>
       <c r="O3">
-        <v>1156.9376547357019</v>
+        <v>1162.4422708049688</v>
       </c>
       <c r="P3">
-        <v>1735.4064821035527</v>
+        <v>1743.6634062074531</v>
       </c>
       <c r="Q3">
-        <v>2313.8753094714039</v>
+        <v>2324.8845416099375</v>
       </c>
       <c r="R3">
-        <v>2892.3441368392541</v>
+        <v>2906.1056770124219</v>
       </c>
       <c r="S3">
-        <v>3470.8129642071053</v>
+        <v>3487.3268124149063</v>
       </c>
     </row>
   </sheetData>
